--- a/data/trans_orig/P34A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34A_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre / solo 2023 en 2023</t>
+          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22766</t>
+          <t>22987</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26349</t>
+          <t>27308</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>25977</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43435</t>
+          <t>44099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>13331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31846</t>
+          <t>30908</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>18579</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>24453</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44231</t>
+          <t>45890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>192793</t>
+          <t>194116</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>233134</t>
+          <t>234244</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>241970</t>
+          <t>242186</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>281717</t>
+          <t>282392</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>451753</t>
+          <t>449593</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>507874</t>
+          <t>505303</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,07%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>138665</t>
+          <t>138107</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>179252</t>
+          <t>176648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>277686</t>
+          <t>277768</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>319646</t>
+          <t>319751</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>427930</t>
+          <t>425838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>485103</t>
+          <t>482636</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86129</t>
+          <t>87709</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122395</t>
+          <t>124209</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>142660</t>
+          <t>141033</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176284</t>
+          <t>175619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>238140</t>
+          <t>238669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>291069</t>
+          <t>288499</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>185742</t>
+          <t>189868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>319415</t>
+          <t>323994</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96010</t>
+          <t>92890</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157421</t>
+          <t>158561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>323677</t>
+          <t>319871</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>468666</t>
+          <t>467022</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>190543</t>
+          <t>195912</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>346334</t>
+          <t>343592</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88013</t>
+          <t>83944</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150632</t>
+          <t>145634</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>337199</t>
+          <t>332184</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>479899</t>
+          <t>475526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>920213</t>
+          <t>918299</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1462893</t>
+          <t>1462241</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1089331</t>
+          <t>1090279</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1488397</t>
+          <t>1501318</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2055153</t>
+          <t>2045999</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2729122</t>
+          <t>2741059</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,63%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>233882</t>
+          <t>242462</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>403912</t>
+          <t>406538</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>288778</t>
+          <t>278034</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>466825</t>
+          <t>467654</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>596535</t>
+          <t>587679</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>837405</t>
+          <t>851415</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>206632</t>
+          <t>210009</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355037</t>
+          <t>355743</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>273970</t>
+          <t>280999</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>433226</t>
+          <t>436201</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>536903</t>
+          <t>554183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>764114</t>
+          <t>769598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97365</t>
+          <t>98802</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140657</t>
+          <t>140848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74129</t>
+          <t>73818</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>105734</t>
+          <t>103880</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>177380</t>
+          <t>178252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>232943</t>
+          <t>233604</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83879</t>
+          <t>85325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128030</t>
+          <t>126920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69175</t>
+          <t>67947</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103183</t>
+          <t>101456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>162596</t>
+          <t>163686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>217754</t>
+          <t>214221</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>247532</t>
+          <t>242996</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>301916</t>
+          <t>299354</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>291377</t>
+          <t>290497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>337054</t>
+          <t>337118</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>555538</t>
+          <t>554278</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>622897</t>
+          <t>625917</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78204</t>
+          <t>81063</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>117667</t>
+          <t>119040</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59740</t>
+          <t>59111</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89165</t>
+          <t>88880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>147315</t>
+          <t>148953</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>196793</t>
+          <t>196790</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40938</t>
+          <t>40838</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69956</t>
+          <t>69724</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83511</t>
+          <t>85737</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>115597</t>
+          <t>116360</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>131911</t>
+          <t>133152</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>174674</t>
+          <t>176770</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>313705</t>
+          <t>310490</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>459631</t>
+          <t>457938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>194518</t>
+          <t>193540</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>274294</t>
+          <t>272549</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>548991</t>
+          <t>547303</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>712724</t>
+          <t>712621</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>315806</t>
+          <t>328541</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>473915</t>
+          <t>473320</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>174673</t>
+          <t>179392</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>250650</t>
+          <t>251548</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>543536</t>
+          <t>539644</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>706003</t>
+          <t>704728</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1402165</t>
+          <t>1402939</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2041600</t>
+          <t>2020579</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1661462</t>
+          <t>1656519</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2122719</t>
+          <t>2124193</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3108346</t>
+          <t>3113867</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3885098</t>
+          <t>3932013</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>475678</t>
+          <t>470559</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>667306</t>
+          <t>672673</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>627535</t>
+          <t>643414</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>842177</t>
+          <t>843579</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1168178</t>
+          <t>1180659</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1475427</t>
+          <t>1480593</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>362493</t>
+          <t>365874</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>514800</t>
+          <t>515083</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>529770</t>
+          <t>521298</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>693375</t>
+          <t>696002</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>933711</t>
+          <t>948986</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1181212</t>
+          <t>1182443</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34A_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>16709</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22987</t>
+          <t>26650</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19112</t>
+          <t>20512</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13507</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27308</t>
+          <t>28571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>33951</t>
+          <t>37220</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25977</t>
+          <t>28044</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44099</t>
+          <t>49378</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20487</t>
+          <t>26727</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13331</t>
+          <t>17011</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30908</t>
+          <t>44321</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12386</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18579</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32873</t>
+          <t>40611</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24453</t>
+          <t>29390</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45890</t>
+          <t>58576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>213899</t>
+          <t>234012</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>194116</t>
+          <t>212451</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>234244</t>
+          <t>255301</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>263009</t>
+          <t>288361</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>242186</t>
+          <t>267375</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>282392</t>
+          <t>307761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>476907</t>
+          <t>522373</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>449593</t>
+          <t>491821</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>505303</t>
+          <t>553678</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>157723</t>
+          <t>170324</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>138107</t>
+          <t>149347</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>176648</t>
+          <t>190357</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>297621</t>
+          <t>322543</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>277768</t>
+          <t>300124</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>319751</t>
+          <t>343838</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>455344</t>
+          <t>492867</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>425838</t>
+          <t>464411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>482636</t>
+          <t>527670</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>104483</t>
+          <t>126732</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87709</t>
+          <t>108876</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124209</t>
+          <t>148295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,67 +1212,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>157465</t>
+          <t>171295</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>141033</t>
+          <t>154248</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>175619</t>
+          <t>190713</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>23,35%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>298028</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>267396</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>325879</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>21,42%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>19,22%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>23,43%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>261948</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>238669</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>288499</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>20,77%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>18,93%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>511431</t>
+          <t>574503</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>511431</t>
+          <t>574503</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>511431</t>
+          <t>574503</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>749593</t>
+          <t>816596</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>749593</t>
+          <t>816596</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>749593</t>
+          <t>816596</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1261024</t>
+          <t>1391099</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1261024</t>
+          <t>1391099</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1261024</t>
+          <t>1391099</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>269786</t>
+          <t>279733</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>189868</t>
+          <t>244356</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>323994</t>
+          <t>321065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>131124</t>
+          <t>147846</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92890</t>
+          <t>123777</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158561</t>
+          <t>170951</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>400910</t>
+          <t>427579</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>319871</t>
+          <t>383322</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>467022</t>
+          <t>477953</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>289444</t>
+          <t>304992</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>195912</t>
+          <t>267795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>343592</t>
+          <t>348058</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>120287</t>
+          <t>129837</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83944</t>
+          <t>107757</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145634</t>
+          <t>151052</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>409731</t>
+          <t>434830</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>332184</t>
+          <t>389941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>475526</t>
+          <t>484820</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1078408</t>
+          <t>933168</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>918299</t>
+          <t>879607</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1462241</t>
+          <t>983468</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1227975</t>
+          <t>1075408</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1090279</t>
+          <t>1026231</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1501318</t>
+          <t>1114720</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2306382</t>
+          <t>2008576</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2045999</t>
+          <t>1940743</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2741059</t>
+          <t>2082664</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>47,4%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>345398</t>
+          <t>370472</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>242462</t>
+          <t>332132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>406538</t>
+          <t>415061</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>383138</t>
+          <t>400118</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>278034</t>
+          <t>369530</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>467654</t>
+          <t>434140</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>728536</t>
+          <t>770591</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>587679</t>
+          <t>718886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>851415</t>
+          <t>826761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>302578</t>
+          <t>337387</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>210009</t>
+          <t>301849</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355743</t>
+          <t>377016</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>373066</t>
+          <t>415184</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>280999</t>
+          <t>382737</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>436201</t>
+          <t>451504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>675643</t>
+          <t>752571</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>554183</t>
+          <t>697652</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>769598</t>
+          <t>803344</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2285614</t>
+          <t>2225753</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2285614</t>
+          <t>2225753</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2285614</t>
+          <t>2225753</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2235589</t>
+          <t>2168394</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2235589</t>
+          <t>2168394</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2235589</t>
+          <t>2168394</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4521202</t>
+          <t>4394147</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4521202</t>
+          <t>4394147</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4521202</t>
+          <t>4394147</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,27 +2089,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>116891</t>
+          <t>131473</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98802</t>
+          <t>108648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140848</t>
+          <t>155022</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>87988</t>
+          <t>92377</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73818</t>
+          <t>76762</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103880</t>
+          <t>108885</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>204879</t>
+          <t>223850</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178252</t>
+          <t>194864</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>233604</t>
+          <t>252916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>103585</t>
+          <t>114194</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85325</t>
+          <t>93521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126920</t>
+          <t>138076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>84401</t>
+          <t>89895</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67947</t>
+          <t>72222</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101456</t>
+          <t>107086</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>187986</t>
+          <t>204089</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>163686</t>
+          <t>176752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>214221</t>
+          <t>234550</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>273903</t>
+          <t>298129</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>242996</t>
+          <t>267797</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>299354</t>
+          <t>327868</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>315042</t>
+          <t>355821</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>290497</t>
+          <t>331526</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>337118</t>
+          <t>380214</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>588945</t>
+          <t>653951</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>554278</t>
+          <t>616663</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>625917</t>
+          <t>690919</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>98367</t>
+          <t>107061</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81063</t>
+          <t>87702</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119040</t>
+          <t>128558</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>72911</t>
+          <t>84877</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59111</t>
+          <t>70600</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88880</t>
+          <t>102318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,27 +2498,27 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>171278</t>
+          <t>191938</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148953</t>
+          <t>167849</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>196790</t>
+          <t>217732</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>52828</t>
+          <t>59602</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40838</t>
+          <t>45581</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69724</t>
+          <t>78343</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>99745</t>
+          <t>111519</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>85737</t>
+          <t>95363</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>116360</t>
+          <t>129904</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>152573</t>
+          <t>171120</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>133152</t>
+          <t>148592</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>176770</t>
+          <t>194693</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>645574</t>
+          <t>710458</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>645574</t>
+          <t>710458</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>645574</t>
+          <t>710458</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660086</t>
+          <t>734489</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660086</t>
+          <t>734489</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660086</t>
+          <t>734489</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1305660</t>
+          <t>1444948</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1305660</t>
+          <t>1444948</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1305660</t>
+          <t>1444948</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>401516</t>
+          <t>427915</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>310490</t>
+          <t>385845</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>457938</t>
+          <t>479838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>238224</t>
+          <t>260734</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>193540</t>
+          <t>229611</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>272549</t>
+          <t>291416</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>639739</t>
+          <t>688649</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>547303</t>
+          <t>633765</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>712621</t>
+          <t>747954</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>413516</t>
+          <t>445913</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>328541</t>
+          <t>394746</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>473320</t>
+          <t>496382</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>217074</t>
+          <t>233617</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>179392</t>
+          <t>204335</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>251548</t>
+          <t>264511</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>630590</t>
+          <t>679530</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>539644</t>
+          <t>624235</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>704728</t>
+          <t>741682</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1566209</t>
+          <t>1465309</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1402939</t>
+          <t>1397507</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2020579</t>
+          <t>1533140</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1806025</t>
+          <t>1719590</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1656519</t>
+          <t>1664361</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2124193</t>
+          <t>1775413</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3372234</t>
+          <t>3184900</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3113867</t>
+          <t>3102932</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3932013</t>
+          <t>3270505</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>601489</t>
+          <t>647857</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>470559</t>
+          <t>605637</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>672673</t>
+          <t>702510</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>753670</t>
+          <t>807539</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>643414</t>
+          <t>763595</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>843579</t>
+          <t>853389</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1355158</t>
+          <t>1455396</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1180659</t>
+          <t>1389674</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1480593</t>
+          <t>1523102</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>459889</t>
+          <t>523721</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>365874</t>
+          <t>478717</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>515083</t>
+          <t>571755</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>630275</t>
+          <t>697998</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>521298</t>
+          <t>657063</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>696002</t>
+          <t>737260</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1090164</t>
+          <t>1221719</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>948986</t>
+          <t>1157376</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1182443</t>
+          <t>1283253</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3442618</t>
+          <t>3510715</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3442618</t>
+          <t>3510715</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3442618</t>
+          <t>3510715</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3645268</t>
+          <t>3719479</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3645268</t>
+          <t>3719479</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3645268</t>
+          <t>3719479</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7087886</t>
+          <t>7230194</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7087886</t>
+          <t>7230194</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7087886</t>
+          <t>7230194</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
